--- a/backend/infacto_participants.xlsx
+++ b/backend/infacto_participants.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,200 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>785</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sfdfgh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Satyam Samal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>scientificsatyam1906@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9692509119</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>fgh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>scientificsatyam1906@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>9692509119</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>xcvb</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>xcghmj</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sfdfgh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Waiting for Assignment...</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>jdhcbygus</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hsbGUTB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jakscbhah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>jibdcs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>kbhdauyvus@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>kadshcv</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>kjbhgtvcyrt</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jdhcbygus</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VWzP7B38</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Waiting for Assignment...</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>

--- a/backend/infacto_participants.xlsx
+++ b/backend/infacto_participants.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,113 @@
       <c r="S6" t="inlineStr">
         <is>
           <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dfgfhgjhkj</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Satyam Samal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scientificsatyam1906@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9692509119</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dsfdgfhgjh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>scientificsatyam1906@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>zxcvbnm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>adsfdgfhgjh</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dfgfhgjhkj</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>D6SkcWTp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Waiting for Assignment...</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>For (Proposition)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1234567890</t>
         </is>
       </c>
     </row>
